--- a/data/daily/2026-07/2026-07-22.xlsx
+++ b/data/daily/2026-07/2026-07-22.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="카카오선물하기" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="다이소몰" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="카테고리통계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="올리브영" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="카테고리통계" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -873,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -881,29 +882,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -911,22 +912,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
     </row>
@@ -941,7 +942,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -951,12 +952,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>48,900원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10848340</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
     </row>
@@ -1031,22 +1032,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>카카오 단독제품 '선물하기 단독' 완전균형영양식 간편한끼 뉴케어 구수한맛 7입+오트아몬드 7입 14개입(1BOX)</t>
+          <t>[특허성분 고농축 숙취해소제] 알디콤A 선물세트 (5포입 x 3개 구성)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>뉴케어</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>25,000원</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13688976</t>
+          <t>https://gift.kakao.com/product/10590720</t>
         </is>
       </c>
     </row>
@@ -1107,29 +1108,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1137,29 +1138,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1167,29 +1168,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1197,12 +1198,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618634&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1228,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안국약품 브이팩 남성용 올인원 멀티 비타민 7포</t>
+          <t>대웅제약 글루타치온 30정 30일분</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1242,7 +1243,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235547&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1257,29 +1258,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>오브맘 면역＆프로폴리스 하루구미 30일분</t>
+          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1287,29 +1288,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 루테인 지아잔틴 30캡슐</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953533&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1317,12 +1318,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1332,7 +1333,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157056&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1347,29 +1348,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>종근당 데일리와이즈 코엔자임Q10 12캡슐 12일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306202&amp;recmYn=N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1377,7 +1378,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1387,12 +1388,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,42 +1419,396 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>비율(%)</t>
+          <t>상품명</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>카카오선물하기</t>
+          <t>브랜드</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>다이소몰</t>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>비비랩 슬림 밸런스 유산균 2 g x 30포 (15일분)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>비비랩</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261097&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>비비랩 데일리 밸런스 유산균 2 g x 30포 (1개월분)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>비비랩</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>16,900원</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[7월 올영픽/단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>비비랩</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>26,900원</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 6종 택1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9,500원</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>39,000원</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>55,900원</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>비율(%)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>카카오선물하기</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>다이소몰</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>46.7</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1463,10 +1818,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>26.7</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1474,6 +1829,9 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1482,53 +1840,62 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1539,34 +1906,128 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/daily/2026-07/2026-07-22.xlsx
+++ b/data/daily/2026-07/2026-07-22.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,11 @@
           <t>상품URL</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -480,6 +485,11 @@
           <t>https://gift.kakao.com/product/2301047</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260720083745_3a4cff6bdbb44f4e9cecf5e36eabe528.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,6 +520,11 @@
           <t>https://gift.kakao.com/product/7608679</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703114353_3ee4124918ae4776af8a6954e0a43f76.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -540,6 +555,11 @@
           <t>https://gift.kakao.com/product/2484405</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260718112704_e8942030fa4b4fee80048cf5f99aba09.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,6 +590,11 @@
           <t>https://gift.kakao.com/product/11866425</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260715133556_5b220cca6be34a0aa6491af5bca27f47.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -600,6 +625,11 @@
           <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +660,11 @@
           <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260629110109_f83c124733904b58826d6a7caacb4073.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -660,6 +695,11 @@
           <t>https://gift.kakao.com/product/7320451</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260720092938_9626171b4b1241379bcc67bbdab37930.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -690,6 +730,11 @@
           <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260720085358_f71eba17fe274d1586a7ac1b6ebd74fb.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -720,6 +765,11 @@
           <t>https://gift.kakao.com/product/5551542</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260513082713_f5025425b9024348b2621639f67a34af.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -750,6 +800,11 @@
           <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -780,6 +835,11 @@
           <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260715133120_23d55d4418d04bcdaf16a351c134e7e8.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -810,6 +870,11 @@
           <t>https://gift.kakao.com/product/13215071</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260714110741_0c5ee4d65772453582e5a95846726854.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -840,6 +905,11 @@
           <t>https://gift.kakao.com/product/13255641</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260714111541_36039105cd90469f9c25fab78362086a.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +940,11 @@
           <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260602111000_0f1c3a6d74c54029b701afe163b8f8ea.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -900,6 +975,11 @@
           <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -930,6 +1010,11 @@
           <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -960,6 +1045,11 @@
           <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -990,6 +1080,11 @@
           <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1020,6 +1115,11 @@
           <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260707130836_45a6a961414d4844a5a8d6ec10e5c825.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1048,6 +1148,11 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>https://gift.kakao.com/product/10590720</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://st.kakaocdn.net/product/gift/product/20260625180125_7d202367d1f745b5871f3fb6bc5bc550.png</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,11 +1201,16 @@
           <t>상품URL</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1108,12 +1218,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1123,14 +1233,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1138,29 +1253,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1168,12 +1288,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1183,14 +1303,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1198,7 +1323,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1208,12 +1333,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1358,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1243,7 +1373,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
     </row>
@@ -1276,11 +1411,16 @@
           <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1288,12 +1428,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1303,14 +1443,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260415/rKimZ2TE65XK1Rwibsnv610910967_00_02rKimZ2TE65XK1Rwibsnv.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1318,29 +1463,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1348,29 +1498,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 코엔자임Q10 12캡슐 12일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306202&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1378,22 +1533,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1602,11 @@
           <t>상품URL</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1472,6 +1637,11 @@
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1502,6 +1672,11 @@
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261097&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026109704ko.png?l=ko</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1532,6 +1707,11 @@
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026108604ko.png?l=ko</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1562,6 +1742,11 @@
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1592,6 +1777,11 @@
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020888833ko.png?l=ko</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1622,6 +1812,11 @@
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786103ko.jpg?l=ko</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1634,22 +1829,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
+          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18,800원</t>
+          <t>29,300원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846223ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1682,11 +1882,16 @@
           <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587409ko.jpg?l=ko</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1694,29 +1899,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308648ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1724,22 +1934,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
+          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>39,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1796,16 +2011,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>32.5</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -1840,16 +2055,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -1902,20 +2117,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1924,7 +2139,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1934,19 +2149,19 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1956,10 +2171,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1968,7 +2183,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1981,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2006,28 +2221,6 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
